--- a/service_evaluation_forms/007_janitorial_services_performance_evaluation--service_evaluation_forms.xlsx
+++ b/service_evaluation_forms/007_janitorial_services_performance_evaluation--service_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>janitorial_services_performance_evaluation</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>janitorial_services_performance_evaluation</t>
+          <t>What is the purpose of this evaluation form?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,46 +538,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>quality_of_services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>How would you rate the overall quality of the services provided?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>areas_met_expectations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>Which areas of the services met your expectations?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,87 +589,87 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>staff_courtesy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>Were the janitorial staff courteous and respectful?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evaluation_category</t>
+          <t>cleanliness_and_organization</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>evaluation_category</t>
+          <t>Did the janitorial staff meet the required standards for cleanliness and organization?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>Would you recommend the services to others?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>next_evaluation_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>What date would you like to schedule the next evaluation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>How would you rate the communication between the janitorial staff and you/your team?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>next_evaluation_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>What time do you expect the next evaluation?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>comments_feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>Do you have any comments or feedback on the services?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,345 +745,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>timeliness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>How would you rate the timeliness of the services?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>staff_equipment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>janitorial_evaluation</t>
+          <t>Are the janitorial staff properly equipped with the necessary cleaning supplies?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,143 +827,143 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quality_of_services_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quality_of_services_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>quality_of_services_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>quality_of_services_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>evaluation_category_choices</t>
+          <t>areas_met_expectations_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>evaluation_category_choices</t>
+          <t>areas_met_expectations_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>areas_met_expectations_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>areas_met_expectations_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>staff_courtesy_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>staff_courtesy_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>cleanliness_and_organization_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>cleanliness_and_organization_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,75 +1065,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>timeliness_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>timeliness_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>timeliness_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>timeliness_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>staff_equipment_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>janitorial_evaluation_choices</t>
+          <t>staff_equipment_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1458,176 +1159,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>janitorial_evaluation_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
